--- a/データ更新用/birds_master_template.xlsx
+++ b/データ更新用/birds_master_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0cfc74c0a86ff0d4/デスクトップ/bird-site/データ更新用/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_5D9FBEA04C9B7583A0C473F14C5BFC1EFAE6C0A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12CB50BD-6E69-4299-959F-9DD25DC625C5}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_5D9FBEA04C9B7583A0C473F14C5BFC1EFAE6C0A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30E7F560-6B3F-43F4-B2D8-CF57CB6989B3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BirdRecords" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
   <si>
     <t>id</t>
   </si>
@@ -168,6 +168,43 @@
     </rPh>
     <rPh sb="3" eb="4">
       <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>family</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アトリ科</t>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ヒタキ科</t>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>科。分類上の科を入れます。</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブンルイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -546,22 +583,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="3" customWidth="1"/>
-    <col min="2" max="2" width="18" style="3" customWidth="1"/>
-    <col min="3" max="3" width="52" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" style="3" customWidth="1"/>
-    <col min="5" max="5" width="18" style="3" customWidth="1"/>
-    <col min="6" max="9" width="12" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14" style="3" customWidth="1"/>
-    <col min="11" max="11" width="28" style="3" customWidth="1"/>
-    <col min="12" max="12" width="18" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="3"/>
+    <col min="2" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="52" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18" style="3" customWidth="1"/>
+    <col min="7" max="10" width="12" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14" style="3" customWidth="1"/>
+    <col min="12" max="12" width="28" style="3" customWidth="1"/>
+    <col min="13" max="13" width="18" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -569,37 +606,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -607,37 +647,40 @@
         <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="4">
+      <c r="E2" s="4">
         <v>46086</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3">
+      <c r="G2" s="3">
         <v>35.025300000000001</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>135.7621</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -645,34 +688,37 @@
         <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="4">
+      <c r="E3" s="4">
         <v>46076</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="3">
+      <c r="G3" s="3">
         <v>34.691031649999999</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>135.79579199</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -680,89 +726,92 @@
         <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="4">
+      <c r="E4" s="4">
         <v>46104</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>35.216549209999997</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>136.84360405999999</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -830,7 +879,7 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="J2:J1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"成鳥オス,成鳥メス,幼鳥オス,幼鳥メス,不明"</formula1>
     </dataValidation>
   </dataValidations>
@@ -840,7 +889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -873,73 +922,81 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>31</v>
       </c>
     </row>
